--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/72.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/72.xlsx
@@ -426,13 +426,13 @@
         <v>-4.152038899058363</v>
       </c>
       <c r="E2">
-        <v>-4.967896559712252</v>
+        <v>-5.317879673395056</v>
       </c>
       <c r="F2">
-        <v>-3.830742126388876</v>
+        <v>-4.125023788070414</v>
       </c>
       <c r="G2">
-        <v>-10.87323306239802</v>
+        <v>-10.42525335056939</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.100465893179301</v>
       </c>
       <c r="E3">
-        <v>-5.497546879649377</v>
+        <v>-5.347178900224684</v>
       </c>
       <c r="F3">
-        <v>-3.530471368385097</v>
+        <v>-4.221338894361316</v>
       </c>
       <c r="G3">
-        <v>-10.78722508928776</v>
+        <v>-10.90946698332535</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.13311503151943</v>
       </c>
       <c r="E4">
-        <v>-5.271440172446397</v>
+        <v>-6.916444583524715</v>
       </c>
       <c r="F4">
-        <v>-3.424905054939731</v>
+        <v>-3.902997301465466</v>
       </c>
       <c r="G4">
-        <v>-11.95470883698498</v>
+        <v>-10.6238562880158</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.23926517817051</v>
       </c>
       <c r="E5">
-        <v>-6.306744428554001</v>
+        <v>-6.642426621320582</v>
       </c>
       <c r="F5">
-        <v>-3.244803899325271</v>
+        <v>-3.908249150799215</v>
       </c>
       <c r="G5">
-        <v>-11.55428511182797</v>
+        <v>-11.54135743149712</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.389177964853967</v>
       </c>
       <c r="E6">
-        <v>-6.242485382385159</v>
+        <v>-7.412624952071149</v>
       </c>
       <c r="F6">
-        <v>-2.980522391503519</v>
+        <v>-3.806402206992418</v>
       </c>
       <c r="G6">
-        <v>-11.80237077344987</v>
+        <v>-11.94492286437089</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.556067885951923</v>
       </c>
       <c r="E7">
-        <v>-7.987958517797653</v>
+        <v>-7.843667750491251</v>
       </c>
       <c r="F7">
-        <v>-2.54893800444056</v>
+        <v>-3.447391916456126</v>
       </c>
       <c r="G7">
-        <v>-11.55682761080213</v>
+        <v>-12.55690369166949</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.715731051273447</v>
       </c>
       <c r="E8">
-        <v>-7.768173560309379</v>
+        <v>-6.734531254162589</v>
       </c>
       <c r="F8">
-        <v>-2.638346183326919</v>
+        <v>-3.049279371038087</v>
       </c>
       <c r="G8">
-        <v>-11.95713546686526</v>
+        <v>-12.31084408391762</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.848132796898175</v>
       </c>
       <c r="E9">
-        <v>-8.967766324941257</v>
+        <v>-8.462732789709827</v>
       </c>
       <c r="F9">
-        <v>-2.503169877068485</v>
+        <v>-2.734530407568178</v>
       </c>
       <c r="G9">
-        <v>-11.30252474465748</v>
+        <v>-12.47072357019118</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.940378976873495</v>
       </c>
       <c r="E10">
-        <v>-8.788239501381174</v>
+        <v>-8.216433616906645</v>
       </c>
       <c r="F10">
-        <v>-2.187236348212573</v>
+        <v>-2.794826442450551</v>
       </c>
       <c r="G10">
-        <v>-11.96920902644699</v>
+        <v>-12.90495789694076</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.993065855707075</v>
       </c>
       <c r="E11">
-        <v>-9.308837401776966</v>
+        <v>-9.6666910032851</v>
       </c>
       <c r="F11">
-        <v>-1.980062489139819</v>
+        <v>-2.516387307347554</v>
       </c>
       <c r="G11">
-        <v>-12.08121802422269</v>
+        <v>-12.79780878001671</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.01222177795263</v>
       </c>
       <c r="E12">
-        <v>-9.828194500294655</v>
+        <v>-10.47572552712545</v>
       </c>
       <c r="F12">
-        <v>-1.747770873679379</v>
+        <v>-2.092959025732558</v>
       </c>
       <c r="G12">
-        <v>-11.61265996132194</v>
+        <v>-12.33201502264125</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.007080421943879</v>
       </c>
       <c r="E13">
-        <v>-9.924587598021926</v>
+        <v>-10.2961624757733</v>
       </c>
       <c r="F13">
-        <v>-1.590495381849059</v>
+        <v>-1.831633961171398</v>
       </c>
       <c r="G13">
-        <v>-11.13379617015744</v>
+        <v>-11.06500634439693</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.995379508039015</v>
       </c>
       <c r="E14">
-        <v>-10.53886151174039</v>
+        <v>-10.71784491841955</v>
       </c>
       <c r="F14">
-        <v>-1.729150831199252</v>
+        <v>-1.492404255846556</v>
       </c>
       <c r="G14">
-        <v>-11.2203603149183</v>
+        <v>-12.06126867680304</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.990836886620249</v>
       </c>
       <c r="E15">
-        <v>-9.669136379249242</v>
+        <v>-11.49057919461441</v>
       </c>
       <c r="F15">
-        <v>-0.9914995994151256</v>
+        <v>-1.644248970984122</v>
       </c>
       <c r="G15">
-        <v>-10.72990961436636</v>
+        <v>-11.39146586111554</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.000695141771218</v>
       </c>
       <c r="E16">
-        <v>-11.02407844471425</v>
+        <v>-11.16094251464807</v>
       </c>
       <c r="F16">
-        <v>-0.8757054336473939</v>
+        <v>-1.351748299218603</v>
       </c>
       <c r="G16">
-        <v>-10.92086188107152</v>
+        <v>-10.93810982333112</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.030585429855652</v>
       </c>
       <c r="E17">
-        <v>-12.85915196684251</v>
+        <v>-13.31564478918572</v>
       </c>
       <c r="F17">
-        <v>-0.6940858805836023</v>
+        <v>-1.250357785850749</v>
       </c>
       <c r="G17">
-        <v>-10.25178738540265</v>
+        <v>-10.60238077910255</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.086053482072592</v>
       </c>
       <c r="E18">
-        <v>-13.33757166033086</v>
+        <v>-13.08359672408468</v>
       </c>
       <c r="F18">
-        <v>-0.4395923619933298</v>
+        <v>-0.6187707163210713</v>
       </c>
       <c r="G18">
-        <v>-9.204019585496559</v>
+        <v>-9.782176569020418</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.168858722132872</v>
       </c>
       <c r="E19">
-        <v>-14.83338096675247</v>
+        <v>-14.00236523007889</v>
       </c>
       <c r="F19">
-        <v>-0.2809020186390285</v>
+        <v>-0.5795119000001943</v>
       </c>
       <c r="G19">
-        <v>-8.815103316634058</v>
+        <v>-9.153189469286589</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.277655200682915</v>
       </c>
       <c r="E20">
-        <v>-14.39085395824892</v>
+        <v>-14.44513224770485</v>
       </c>
       <c r="F20">
-        <v>-0.02079962436440054</v>
+        <v>-0.1406792981627394</v>
       </c>
       <c r="G20">
-        <v>-8.513539102370768</v>
+        <v>-8.773314300291839</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.417632689596936</v>
       </c>
       <c r="E21">
-        <v>-15.12145531227641</v>
+        <v>-15.62890252415393</v>
       </c>
       <c r="F21">
-        <v>0.03505801797377293</v>
+        <v>-0.04261882175413952</v>
       </c>
       <c r="G21">
-        <v>-7.202347883359325</v>
+        <v>-8.208909322938112</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.585266455160949</v>
       </c>
       <c r="E22">
-        <v>-16.29002350148174</v>
+        <v>-16.33651734411849</v>
       </c>
       <c r="F22">
-        <v>0.2756291656251941</v>
+        <v>-0.3396349242323191</v>
       </c>
       <c r="G22">
-        <v>-7.081191848258618</v>
+        <v>-7.539834827269248</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.772218011219156</v>
       </c>
       <c r="E23">
-        <v>-17.40975662698835</v>
+        <v>-16.79475815742866</v>
       </c>
       <c r="F23">
-        <v>0.540619755943742</v>
+        <v>0.1112346843352155</v>
       </c>
       <c r="G23">
-        <v>-6.767050871491636</v>
+        <v>-7.475256015434685</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.977374122981428</v>
       </c>
       <c r="E24">
-        <v>-17.41525872290767</v>
+        <v>-17.87409276631285</v>
       </c>
       <c r="F24">
-        <v>0.5778449302907461</v>
+        <v>0.4372030559086405</v>
       </c>
       <c r="G24">
-        <v>-6.589939995686166</v>
+        <v>-6.760880014606434</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.199457121975125</v>
       </c>
       <c r="E25">
-        <v>-17.84536865568219</v>
+        <v>-18.9894785567721</v>
       </c>
       <c r="F25">
-        <v>0.6744955253797813</v>
+        <v>0.1076992122600672</v>
       </c>
       <c r="G25">
-        <v>-6.900472477815343</v>
+        <v>-7.046964117928093</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.438886353943033</v>
       </c>
       <c r="E26">
-        <v>-17.86737251088547</v>
+        <v>-18.00621552396064</v>
       </c>
       <c r="F26">
-        <v>0.4214914113797423</v>
+        <v>0.3276241307641135</v>
       </c>
       <c r="G26">
-        <v>-5.980187165535503</v>
+        <v>-6.309298429231069</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.696248681794028</v>
       </c>
       <c r="E27">
-        <v>-19.50901679425009</v>
+        <v>-18.69436243416623</v>
       </c>
       <c r="F27">
-        <v>0.2807526180115091</v>
+        <v>0.1631045659963121</v>
       </c>
       <c r="G27">
-        <v>-5.447020495890339</v>
+        <v>-6.246136530887314</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.971528162928622</v>
       </c>
       <c r="E28">
-        <v>-17.76435425568497</v>
+        <v>-18.59200986464486</v>
       </c>
       <c r="F28">
-        <v>-0.004290262026606392</v>
+        <v>0.1065991403491494</v>
       </c>
       <c r="G28">
-        <v>-6.051271199354733</v>
+        <v>-6.523139807794752</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.258572071719538</v>
       </c>
       <c r="E29">
-        <v>-18.55387558502627</v>
+        <v>-18.23625294660228</v>
       </c>
       <c r="F29">
-        <v>-0.007532492041163657</v>
+        <v>0.3252624552987321</v>
       </c>
       <c r="G29">
-        <v>-5.692941060729559</v>
+        <v>-6.972129236012868</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.545659458895911</v>
       </c>
       <c r="E30">
-        <v>-18.42788438118486</v>
+        <v>-18.15625745325678</v>
       </c>
       <c r="F30">
-        <v>-0.01716060636390231</v>
+        <v>-0.1611797346472215</v>
       </c>
       <c r="G30">
-        <v>-5.757930380210992</v>
+        <v>-5.93063823044923</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.830905034917632</v>
       </c>
       <c r="E31">
-        <v>-17.78480484430361</v>
+        <v>-18.01611929661541</v>
       </c>
       <c r="F31">
-        <v>-0.2504048443375619</v>
+        <v>-0.6350141727225668</v>
       </c>
       <c r="G31">
-        <v>-5.484005910655076</v>
+        <v>-6.826975056297983</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.108137212784223</v>
       </c>
       <c r="E32">
-        <v>-18.79549684417953</v>
+        <v>-18.5591467287712</v>
       </c>
       <c r="F32">
-        <v>-0.3283873516371074</v>
+        <v>-0.6024311693008511</v>
       </c>
       <c r="G32">
-        <v>-5.58146837133122</v>
+        <v>-6.060514242500378</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.359388279216061</v>
       </c>
       <c r="E33">
-        <v>-18.43827270055846</v>
+        <v>-18.04097609044351</v>
       </c>
       <c r="F33">
-        <v>-0.3339796599734068</v>
+        <v>-0.3198096071811185</v>
       </c>
       <c r="G33">
-        <v>-5.069555404048177</v>
+        <v>-5.848139435610593</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.568371338079945</v>
       </c>
       <c r="E34">
-        <v>-17.48025591033976</v>
+        <v>-17.65561200933879</v>
       </c>
       <c r="F34">
-        <v>-0.3644296173329138</v>
+        <v>-0.2254270820409484</v>
       </c>
       <c r="G34">
-        <v>-5.859153620619748</v>
+        <v>-5.500396421620008</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.720810816517112</v>
       </c>
       <c r="E35">
-        <v>-17.08065430695492</v>
+        <v>-17.84285535260794</v>
       </c>
       <c r="F35">
-        <v>-0.2608281913669881</v>
+        <v>-0.5049546919112248</v>
       </c>
       <c r="G35">
-        <v>-5.517243787869359</v>
+        <v>-5.915846712979767</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.802340921803694</v>
       </c>
       <c r="E36">
-        <v>-17.0119799986286</v>
+        <v>-17.52783205826435</v>
       </c>
       <c r="F36">
-        <v>-0.189992009651394</v>
+        <v>-0.6116210772675087</v>
       </c>
       <c r="G36">
-        <v>-5.380895659288936</v>
+        <v>-6.492891353202431</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.803165440990048</v>
       </c>
       <c r="E37">
-        <v>-16.63609854209593</v>
+        <v>-16.97913044817696</v>
       </c>
       <c r="F37">
-        <v>-0.6195916284172456</v>
+        <v>-0.9995554724073508</v>
       </c>
       <c r="G37">
-        <v>-5.241687219362582</v>
+        <v>-6.01857956215443</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.723376550178179</v>
       </c>
       <c r="E38">
-        <v>-16.15617539523703</v>
+        <v>-16.45716947710486</v>
       </c>
       <c r="F38">
-        <v>-0.2890548106173813</v>
+        <v>-0.6144060484757207</v>
       </c>
       <c r="G38">
-        <v>-5.026448790581327</v>
+        <v>-5.360747679136932</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.565555923371479</v>
       </c>
       <c r="E39">
-        <v>-14.80976497480247</v>
+        <v>-17.61377796645592</v>
       </c>
       <c r="F39">
-        <v>-0.5208883389040733</v>
+        <v>-0.1538172051711396</v>
       </c>
       <c r="G39">
-        <v>-4.496943584302597</v>
+        <v>-5.341069796451504</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.333901332848447</v>
       </c>
       <c r="E40">
-        <v>-15.95310503531107</v>
+        <v>-15.9963972468244</v>
       </c>
       <c r="F40">
-        <v>-0.4112340323258915</v>
+        <v>-0.7784990040310803</v>
       </c>
       <c r="G40">
-        <v>-4.856055011675039</v>
+        <v>-6.022747538988373</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.044046782307435</v>
       </c>
       <c r="E41">
-        <v>-15.45241430665299</v>
+        <v>-16.1808374646828</v>
       </c>
       <c r="F41">
-        <v>-0.1800549142874111</v>
+        <v>-0.7327234213523797</v>
       </c>
       <c r="G41">
-        <v>-3.829494566493515</v>
+        <v>-5.451880376741989</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.709490459380044</v>
       </c>
       <c r="E42">
-        <v>-14.9711326175918</v>
+        <v>-15.73325215071268</v>
       </c>
       <c r="F42">
-        <v>-0.3537718423284954</v>
+        <v>-0.6177775038051146</v>
       </c>
       <c r="G42">
-        <v>-4.245477855685097</v>
+        <v>-5.329016100143017</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.340193771401742</v>
       </c>
       <c r="E43">
-        <v>-15.15301877610988</v>
+        <v>-15.43893756800617</v>
       </c>
       <c r="F43">
-        <v>-0.3491677763037357</v>
+        <v>-0.2906552164395899</v>
       </c>
       <c r="G43">
-        <v>-4.642802910217346</v>
+        <v>-5.260126958016323</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.947752207907569</v>
       </c>
       <c r="E44">
-        <v>-14.00985985456159</v>
+        <v>-14.62575496197479</v>
       </c>
       <c r="F44">
-        <v>-0.4607397534193984</v>
+        <v>-0.8944986049147063</v>
       </c>
       <c r="G44">
-        <v>-4.322795646754775</v>
+        <v>-4.615775616434736</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.541024999813612</v>
       </c>
       <c r="E45">
-        <v>-13.5967769840559</v>
+        <v>-14.55643761033938</v>
       </c>
       <c r="F45">
-        <v>-0.0915678799529651</v>
+        <v>-0.7027067001445367</v>
       </c>
       <c r="G45">
-        <v>-4.234665613953837</v>
+        <v>-4.413550942168356</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.12436181350653</v>
       </c>
       <c r="E46">
-        <v>-13.75598454474357</v>
+        <v>-14.06663786166976</v>
       </c>
       <c r="F46">
-        <v>-0.5088803250330917</v>
+        <v>-1.108208282795548</v>
       </c>
       <c r="G46">
-        <v>-3.625356396905436</v>
+        <v>-4.57056018545937</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.700603369853046</v>
       </c>
       <c r="E47">
-        <v>-13.66692304643472</v>
+        <v>-14.04941154654458</v>
       </c>
       <c r="F47">
-        <v>-0.2083204668057358</v>
+        <v>-1.106073579998534</v>
       </c>
       <c r="G47">
-        <v>-2.987089838025029</v>
+        <v>-4.107530733609206</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.279072513189201</v>
       </c>
       <c r="E48">
-        <v>-14.13836888995126</v>
+        <v>-13.61959143610655</v>
       </c>
       <c r="F48">
-        <v>-0.6370329040831891</v>
+        <v>-0.7976906200191393</v>
       </c>
       <c r="G48">
-        <v>-3.431954326501213</v>
+        <v>-4.219675463752017</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.868301974503923</v>
       </c>
       <c r="E49">
-        <v>-12.55361582554499</v>
+        <v>-13.16581116969393</v>
       </c>
       <c r="F49">
-        <v>-0.8900353613484225</v>
+        <v>-1.338899492433779</v>
       </c>
       <c r="G49">
-        <v>-3.975314165861793</v>
+        <v>-4.096639038785003</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.471935214824732</v>
       </c>
       <c r="E50">
-        <v>-12.96232419015926</v>
+        <v>-12.91472992833865</v>
       </c>
       <c r="F50">
-        <v>-0.765622032754562</v>
+        <v>-1.219411636416965</v>
       </c>
       <c r="G50">
-        <v>-3.899846969748567</v>
+        <v>-4.106716339406545</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.101875875706944</v>
       </c>
       <c r="E51">
-        <v>-11.79417262056264</v>
+        <v>-13.08176722058558</v>
       </c>
       <c r="F51">
-        <v>-0.9412135562281816</v>
+        <v>-1.275396847335169</v>
       </c>
       <c r="G51">
-        <v>-2.856280252131807</v>
+        <v>-3.914747735220827</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.76694509771583</v>
       </c>
       <c r="E52">
-        <v>-11.88618215545049</v>
+        <v>-12.20884498544502</v>
       </c>
       <c r="F52">
-        <v>-1.000366444094692</v>
+        <v>-1.360437873273969</v>
       </c>
       <c r="G52">
-        <v>-3.225992046320996</v>
+        <v>-4.02120825867271</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.472819971471837</v>
       </c>
       <c r="E53">
-        <v>-10.97503054273717</v>
+        <v>-11.94154727866827</v>
       </c>
       <c r="F53">
-        <v>-1.117012171552501</v>
+        <v>-1.396181098337365</v>
       </c>
       <c r="G53">
-        <v>-3.126102955764566</v>
+        <v>-3.689349242179548</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.226169573013779</v>
       </c>
       <c r="E54">
-        <v>-10.66122993637566</v>
+        <v>-12.60590611491156</v>
       </c>
       <c r="F54">
-        <v>-0.9067808083960146</v>
+        <v>-1.125555952944975</v>
       </c>
       <c r="G54">
-        <v>-3.480801425933159</v>
+        <v>-4.126553128277858</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.03241862443022</v>
       </c>
       <c r="E55">
-        <v>-10.97678306217814</v>
+        <v>-11.61256269895903</v>
       </c>
       <c r="F55">
-        <v>-1.074949331573148</v>
+        <v>-1.241716257104744</v>
       </c>
       <c r="G55">
-        <v>-3.156924134735181</v>
+        <v>-4.332161180085373</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.887028513772176</v>
       </c>
       <c r="E56">
-        <v>-10.54179596289736</v>
+        <v>-12.08236923488479</v>
       </c>
       <c r="F56">
-        <v>-1.088919747821361</v>
+        <v>-1.263064941809693</v>
       </c>
       <c r="G56">
-        <v>-4.150005032878055</v>
+        <v>-3.743946759213209</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.77780637620528</v>
       </c>
       <c r="E57">
-        <v>-10.72934724239903</v>
+        <v>-10.8388457439045</v>
       </c>
       <c r="F57">
-        <v>-1.016313344965985</v>
+        <v>-1.677580818537969</v>
       </c>
       <c r="G57">
-        <v>-3.637069107023378</v>
+        <v>-4.038370126748291</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.697750728523636</v>
       </c>
       <c r="E58">
-        <v>-10.14321779463824</v>
+        <v>-9.765085686523761</v>
       </c>
       <c r="F58">
-        <v>-0.9175595250412417</v>
+        <v>-1.293654893260273</v>
       </c>
       <c r="G58">
-        <v>-4.346515705543654</v>
+        <v>-4.864165848246254</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.643020187089574</v>
       </c>
       <c r="E59">
-        <v>-10.30282838951259</v>
+        <v>-10.34379749385999</v>
       </c>
       <c r="F59">
-        <v>-1.374887085881001</v>
+        <v>-1.459173469115851</v>
       </c>
       <c r="G59">
-        <v>-4.204456885907987</v>
+        <v>-5.582961427369431</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.610949612723184</v>
       </c>
       <c r="E60">
-        <v>-9.397862672293757</v>
+        <v>-10.8057244850124</v>
       </c>
       <c r="F60">
-        <v>-0.9336190838793158</v>
+        <v>-1.438789004067761</v>
       </c>
       <c r="G60">
-        <v>-4.241243667940369</v>
+        <v>-4.747886246724892</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.601345449999575</v>
       </c>
       <c r="E61">
-        <v>-10.26263365422051</v>
+        <v>-10.13801910647744</v>
       </c>
       <c r="F61">
-        <v>-1.005378066881629</v>
+        <v>-1.430657749641881</v>
       </c>
       <c r="G61">
-        <v>-4.449794794732297</v>
+        <v>-4.853714455978774</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.61082507831947</v>
       </c>
       <c r="E62">
-        <v>-9.757618232885113</v>
+        <v>-10.04571522077909</v>
       </c>
       <c r="F62">
-        <v>-1.025210839239454</v>
+        <v>-1.565549097513752</v>
       </c>
       <c r="G62">
-        <v>-4.695136014102145</v>
+        <v>-5.594935670584976</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.631295493494601</v>
       </c>
       <c r="E63">
-        <v>-8.868266694044724</v>
+        <v>-10.4375595481888</v>
       </c>
       <c r="F63">
-        <v>-0.9392967140581036</v>
+        <v>-1.673161478444033</v>
       </c>
       <c r="G63">
-        <v>-5.452218052386995</v>
+        <v>-5.161085367117947</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.65468544593549</v>
       </c>
       <c r="E64">
-        <v>-9.16793846150231</v>
+        <v>-9.700568517336482</v>
       </c>
       <c r="F64">
-        <v>-0.9376847110922557</v>
+        <v>-1.640631490536097</v>
       </c>
       <c r="G64">
-        <v>-5.333280082797598</v>
+        <v>-5.715230963845473</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.675664113329713</v>
       </c>
       <c r="E65">
-        <v>-9.679135249858177</v>
+        <v>-10.89202361417658</v>
       </c>
       <c r="F65">
-        <v>-1.267234114947983</v>
+        <v>-1.668715630593208</v>
       </c>
       <c r="G65">
-        <v>-5.695903998987207</v>
+        <v>-5.265238440328957</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.688615759834481</v>
       </c>
       <c r="E66">
-        <v>-9.733051261393502</v>
+        <v>-10.52178010778345</v>
       </c>
       <c r="F66">
-        <v>-1.027965160853763</v>
+        <v>-1.792963285706509</v>
       </c>
       <c r="G66">
-        <v>-5.200073661933944</v>
+        <v>-5.799242677995557</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.686581935917541</v>
       </c>
       <c r="E67">
-        <v>-9.881490110890928</v>
+        <v>-10.27923956840664</v>
       </c>
       <c r="F67">
-        <v>-1.054723084698992</v>
+        <v>-1.531607571551445</v>
       </c>
       <c r="G67">
-        <v>-5.769984076519479</v>
+        <v>-5.793085063292513</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.664985909915598</v>
       </c>
       <c r="E68">
-        <v>-8.885126202775281</v>
+        <v>-10.90672304080547</v>
       </c>
       <c r="F68">
-        <v>-0.7217906283702318</v>
+        <v>-1.852256996031495</v>
       </c>
       <c r="G68">
-        <v>-5.216815090726038</v>
+        <v>-5.833013553041662</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.616892311105209</v>
       </c>
       <c r="E69">
-        <v>-9.183140548746058</v>
+        <v>-10.34700818193143</v>
       </c>
       <c r="F69">
-        <v>-0.9179811640492667</v>
+        <v>-1.919790476912127</v>
       </c>
       <c r="G69">
-        <v>-5.2264388466087</v>
+        <v>-6.182772689265663</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.535023149206398</v>
       </c>
       <c r="E70">
-        <v>-10.31720176601294</v>
+        <v>-10.10054145558996</v>
       </c>
       <c r="F70">
-        <v>-1.26650515163352</v>
+        <v>-1.847285134879892</v>
       </c>
       <c r="G70">
-        <v>-5.70624945379743</v>
+        <v>-5.796147317916339</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.416564964464236</v>
       </c>
       <c r="E71">
-        <v>-10.47147781850625</v>
+        <v>-10.9528455485736</v>
       </c>
       <c r="F71">
-        <v>-0.8613680506397401</v>
+        <v>-1.869960864164126</v>
       </c>
       <c r="G71">
-        <v>-5.704441895932987</v>
+        <v>-5.808684353873558</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.262741806345665</v>
       </c>
       <c r="E72">
-        <v>-10.06435441979466</v>
+        <v>-11.09533851169895</v>
       </c>
       <c r="F72">
-        <v>-0.9402543067757398</v>
+        <v>-1.850227495894636</v>
       </c>
       <c r="G72">
-        <v>-5.764534918561838</v>
+        <v>-5.869489143793353</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.077688038109381</v>
       </c>
       <c r="E73">
-        <v>-10.43107930188383</v>
+        <v>-11.40444309051452</v>
       </c>
       <c r="F73">
-        <v>-0.9533648776598476</v>
+        <v>-1.620541924283403</v>
       </c>
       <c r="G73">
-        <v>-4.548041854701248</v>
+        <v>-6.192045527321162</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.869137953865719</v>
       </c>
       <c r="E74">
-        <v>-11.80494133175288</v>
+        <v>-11.6381666909984</v>
       </c>
       <c r="F74">
-        <v>-1.031040060652954</v>
+        <v>-2.233450965614757</v>
       </c>
       <c r="G74">
-        <v>-5.188721801279783</v>
+        <v>-5.732763613021453</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.647018494383334</v>
       </c>
       <c r="E75">
-        <v>-11.89959549546121</v>
+        <v>-10.76612297981533</v>
       </c>
       <c r="F75">
-        <v>-1.285958531720863</v>
+        <v>-2.115184123149669</v>
       </c>
       <c r="G75">
-        <v>-5.057846004475775</v>
+        <v>-5.923825127729411</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.421998216330051</v>
       </c>
       <c r="E76">
-        <v>-10.87339800058303</v>
+        <v>-11.93116801624268</v>
       </c>
       <c r="F76">
-        <v>-1.170751678441716</v>
+        <v>-2.285735030977254</v>
       </c>
       <c r="G76">
-        <v>-5.052691485071129</v>
+        <v>-5.935332584023917</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.203512862747861</v>
       </c>
       <c r="E77">
-        <v>-11.02714875009145</v>
+        <v>-12.4794665921434</v>
       </c>
       <c r="F77">
-        <v>-1.246839709491059</v>
+        <v>-2.301464899589013</v>
       </c>
       <c r="G77">
-        <v>-4.434145845968162</v>
+        <v>-5.213938226652411</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.001389954282992</v>
       </c>
       <c r="E78">
-        <v>-12.88231963986575</v>
+        <v>-13.65018580650237</v>
       </c>
       <c r="F78">
-        <v>-1.420761244280635</v>
+        <v>-2.050721400231214</v>
       </c>
       <c r="G78">
-        <v>-4.910443964339725</v>
+        <v>-5.61435533071834</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.8242346930851475</v>
       </c>
       <c r="E79">
-        <v>-12.53013568781522</v>
+        <v>-13.80183987254524</v>
       </c>
       <c r="F79">
-        <v>-1.245400835312396</v>
+        <v>-2.250699231675848</v>
       </c>
       <c r="G79">
-        <v>-4.711582804341244</v>
+        <v>-5.322954491260612</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.676854372866847</v>
       </c>
       <c r="E80">
-        <v>-14.59780522039945</v>
+        <v>-14.35117546899371</v>
       </c>
       <c r="F80">
-        <v>-1.520936542668582</v>
+        <v>-2.319576324483822</v>
       </c>
       <c r="G80">
-        <v>-4.220966576512333</v>
+        <v>-4.81971184274492</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.5635032987476929</v>
       </c>
       <c r="E81">
-        <v>-14.32574355896663</v>
+        <v>-13.6092891577391</v>
       </c>
       <c r="F81">
-        <v>-1.618099068812547</v>
+        <v>-2.092395735898655</v>
       </c>
       <c r="G81">
-        <v>-4.847099985991311</v>
+        <v>-4.880178957019708</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.4872168691298311</v>
       </c>
       <c r="E82">
-        <v>-15.30019418135916</v>
+        <v>-15.11467165821292</v>
       </c>
       <c r="F82">
-        <v>-1.190472621200164</v>
+        <v>-2.322505431620121</v>
       </c>
       <c r="G82">
-        <v>-4.059352364376192</v>
+        <v>-4.855114816741886</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.44779315959678</v>
       </c>
       <c r="E83">
-        <v>-16.815032135561</v>
+        <v>-17.22446958449051</v>
       </c>
       <c r="F83">
-        <v>-1.386328496448468</v>
+        <v>-2.546101674453375</v>
       </c>
       <c r="G83">
-        <v>-3.830421519244511</v>
+        <v>-3.772616083583297</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.4427075316126136</v>
       </c>
       <c r="E84">
-        <v>-17.88387427016941</v>
+        <v>-18.0276216205949</v>
       </c>
       <c r="F84">
-        <v>-1.708016693651628</v>
+        <v>-2.477778759437874</v>
       </c>
       <c r="G84">
-        <v>-4.110258623133565</v>
+        <v>-3.961919698609902</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.4722524958496901</v>
       </c>
       <c r="E85">
-        <v>-17.53887700636906</v>
+        <v>-18.93074424889261</v>
       </c>
       <c r="F85">
-        <v>-1.729210473652253</v>
+        <v>-2.762304738216643</v>
       </c>
       <c r="G85">
-        <v>-3.851036286317553</v>
+        <v>-4.208144833638736</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.5360725350339665</v>
       </c>
       <c r="E86">
-        <v>-19.31504413860554</v>
+        <v>-18.76953057421954</v>
       </c>
       <c r="F86">
-        <v>-2.105087981244349</v>
+        <v>-2.716341944504909</v>
       </c>
       <c r="G86">
-        <v>-3.55602033113094</v>
+        <v>-3.764717121926596</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.6334394736029924</v>
       </c>
       <c r="E87">
-        <v>-20.40168770453811</v>
+        <v>-20.62228778734776</v>
       </c>
       <c r="F87">
-        <v>-1.657661895970252</v>
+        <v>-2.5804333614624</v>
       </c>
       <c r="G87">
-        <v>-3.421817436059965</v>
+        <v>-3.459878778124966</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.7667911011707719</v>
       </c>
       <c r="E88">
-        <v>-21.9772479667088</v>
+        <v>-21.89522824548187</v>
       </c>
       <c r="F88">
-        <v>-1.871019517704904</v>
+        <v>-2.704261862669884</v>
       </c>
       <c r="G88">
-        <v>-3.998991187558661</v>
+        <v>-4.097711655539728</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.9374376976132791</v>
       </c>
       <c r="E89">
-        <v>-23.42683061046011</v>
+        <v>-23.20986689227862</v>
       </c>
       <c r="F89">
-        <v>-2.057275443122164</v>
+        <v>-2.880018231256661</v>
       </c>
       <c r="G89">
-        <v>-3.42297612699871</v>
+        <v>-3.884644944632234</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.144768343318097</v>
       </c>
       <c r="E90">
-        <v>-25.31827910550986</v>
+        <v>-25.66554513478806</v>
       </c>
       <c r="F90">
-        <v>-1.970780632391451</v>
+        <v>-2.773570534894716</v>
       </c>
       <c r="G90">
-        <v>-3.059137240596189</v>
+        <v>-4.140613015183143</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.388208015214575</v>
       </c>
       <c r="E91">
-        <v>-26.53446419890584</v>
+        <v>-26.0979691177805</v>
       </c>
       <c r="F91">
-        <v>-2.137715716505816</v>
+        <v>-2.900570026520116</v>
       </c>
       <c r="G91">
-        <v>-3.452396945206213</v>
+        <v>-3.93412766880772</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.667482124326332</v>
       </c>
       <c r="E92">
-        <v>-28.24362802972483</v>
+        <v>-28.03956140551718</v>
       </c>
       <c r="F92">
-        <v>-1.929301791431071</v>
+        <v>-3.114455318290352</v>
       </c>
       <c r="G92">
-        <v>-3.229484671864927</v>
+        <v>-4.093593336888874</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.97979784299167</v>
       </c>
       <c r="E93">
-        <v>-30.32600831012298</v>
+        <v>-30.68860322391714</v>
       </c>
       <c r="F93">
-        <v>-1.828532553615317</v>
+        <v>-2.676054295869756</v>
       </c>
       <c r="G93">
-        <v>-3.527433770399333</v>
+        <v>-4.219903891394227</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.319749721796409</v>
       </c>
       <c r="E94">
-        <v>-32.31152679573406</v>
+        <v>-33.11411050835049</v>
       </c>
       <c r="F94">
-        <v>-1.712716850295112</v>
+        <v>-3.330577202048146</v>
       </c>
       <c r="G94">
-        <v>-4.248649358311718</v>
+        <v>-4.094953971105515</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.683714554968236</v>
       </c>
       <c r="E95">
-        <v>-34.91191921786962</v>
+        <v>-34.43839933325757</v>
       </c>
       <c r="F95">
-        <v>-1.927384949260993</v>
+        <v>-3.218236499982685</v>
       </c>
       <c r="G95">
-        <v>-3.72018366333232</v>
+        <v>-4.353395019174259</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.061741135484159</v>
       </c>
       <c r="E96">
-        <v>-37.64241243400855</v>
+        <v>-37.33511698055905</v>
       </c>
       <c r="F96">
-        <v>-2.065805970636193</v>
+        <v>-3.04097747292723</v>
       </c>
       <c r="G96">
-        <v>-4.670366512377318</v>
+        <v>-4.96284327913531</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.438486424204308</v>
       </c>
       <c r="E97">
-        <v>-38.30319604002279</v>
+        <v>-38.75468716282453</v>
       </c>
       <c r="F97">
-        <v>-1.727497409863264</v>
+        <v>-2.948977332437511</v>
       </c>
       <c r="G97">
-        <v>-4.918452173999222</v>
+        <v>-5.002397677238521</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.797129281881045</v>
       </c>
       <c r="E98">
-        <v>-41.56364298385736</v>
+        <v>-41.51066889491563</v>
       </c>
       <c r="F98">
-        <v>-2.095205558128951</v>
+        <v>-2.738618400700993</v>
       </c>
       <c r="G98">
-        <v>-4.976260920205976</v>
+        <v>-5.387788215101699</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.119107497480024</v>
       </c>
       <c r="E99">
-        <v>-44.71148942149119</v>
+        <v>-43.80710108470834</v>
       </c>
       <c r="F99">
-        <v>-1.756504351207094</v>
+        <v>-3.030216151997462</v>
       </c>
       <c r="G99">
-        <v>-5.05246305742892</v>
+        <v>-5.329297496513855</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.38336622023274</v>
       </c>
       <c r="E100">
-        <v>-46.45740861159344</v>
+        <v>-46.4210155302308</v>
       </c>
       <c r="F100">
-        <v>-1.649755957477933</v>
+        <v>-2.770590068979443</v>
       </c>
       <c r="G100">
-        <v>-5.976068846884649</v>
+        <v>-5.970361466374945</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.572672109765828</v>
       </c>
       <c r="E101">
-        <v>-48.04698450081788</v>
+        <v>-49.12626250377697</v>
       </c>
       <c r="F101">
-        <v>-1.405358580792981</v>
+        <v>-2.692968729867518</v>
       </c>
       <c r="G101">
-        <v>-6.227273042404547</v>
+        <v>-6.625326416955436</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.672107135733136</v>
       </c>
       <c r="E102">
-        <v>-50.51883618824571</v>
+        <v>-50.38440843732802</v>
       </c>
       <c r="F102">
-        <v>-1.425019881098427</v>
+        <v>-2.703208179333523</v>
       </c>
       <c r="G102">
-        <v>-6.749571191044284</v>
+        <v>-7.362171090358721</v>
       </c>
     </row>
   </sheetData>
